--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="527">
   <si>
     <t>Filename</t>
   </si>
@@ -826,16 +826,22 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9613,0.0024,0.0111,0.0026</t>
-  </si>
-  <si>
-    <t>0.0030,0.0041,0.0006,0.9993</t>
-  </si>
-  <si>
-    <t>0.9726,0.0022,0.0009,0.0110</t>
-  </si>
-  <si>
-    <t>0.0879,0.0015,0.0048,0.9541</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9614,0.0024,0.0111,0.0026</t>
+  </si>
+  <si>
+    <t>0.0030,0.0042,0.0006,0.9993</t>
+  </si>
+  <si>
+    <t>0.9727,0.0023,0.0008,0.0110</t>
+  </si>
+  <si>
+    <t>0.0882,0.0015,0.0048,0.9539</t>
   </si>
   <si>
     <t>0.9925,0.0020,0.0020,0.0005</t>
@@ -850,10 +856,10 @@
     <t>0.9906,0.0021,0.0024,0.0001</t>
   </si>
   <si>
-    <t>0.9816,0.0149,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9882,0.0066,0.0022,0.0011</t>
+    <t>0.9816,0.0150,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9882,0.0067,0.0022,0.0011</t>
   </si>
   <si>
     <t>0.9932,0.0013,0.0014,0.0001</t>
@@ -862,49 +868,49 @@
     <t>0.9929,0.0021,0.0019,0.0004</t>
   </si>
   <si>
-    <t>0.8131,0.0069,0.1753,0.0026</t>
+    <t>0.8134,0.0070,0.1748,0.0026</t>
   </si>
   <si>
     <t>0.0162,0.0125,0.9777,0.0008</t>
   </si>
   <si>
-    <t>0.2571,0.0004,0.8678,0.0001</t>
-  </si>
-  <si>
-    <t>0.0433,0.0092,0.9567,0.0009</t>
-  </si>
-  <si>
-    <t>0.6920,0.0006,0.3823,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.9975,0.0179,0.0013</t>
+    <t>0.2575,0.0004,0.8676,0.0001</t>
+  </si>
+  <si>
+    <t>0.0434,0.0092,0.9565,0.0009</t>
+  </si>
+  <si>
+    <t>0.6934,0.0006,0.3804,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.9975,0.0178,0.0013</t>
   </si>
   <si>
     <t>0.0028,0.9964,0.0064,0.0019</t>
   </si>
   <si>
-    <t>0.0343,0.9933,0.0080,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.9940,0.0085,0.0031</t>
-  </si>
-  <si>
-    <t>0.0010,0.9993,0.0155,0.0001</t>
-  </si>
-  <si>
-    <t>0.3570,0.0022,0.7336,0.0023</t>
-  </si>
-  <si>
-    <t>0.1140,0.0090,0.9075,0.0020</t>
-  </si>
-  <si>
-    <t>0.0166,0.0004,0.9923,0.0000</t>
+    <t>0.0342,0.9933,0.0079,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.9940,0.0084,0.0031</t>
+  </si>
+  <si>
+    <t>0.0010,0.9993,0.0154,0.0001</t>
+  </si>
+  <si>
+    <t>0.3580,0.0022,0.7327,0.0023</t>
+  </si>
+  <si>
+    <t>0.1145,0.0091,0.9071,0.0020</t>
+  </si>
+  <si>
+    <t>0.0167,0.0004,0.9923,0.0000</t>
   </si>
   <si>
     <t>0.0190,0.0026,0.9857,0.0003</t>
   </si>
   <si>
-    <t>0.0280,0.0014,0.9842,0.0003</t>
+    <t>0.0281,0.0014,0.9842,0.0003</t>
   </si>
   <si>
     <t>0.0540,0.0009,0.9701,0.0002</t>
@@ -913,112 +919,112 @@
     <t>0.0117,0.0010,0.9922,0.0002</t>
   </si>
   <si>
-    <t>0.7467,0.1045,0.0789,0.0022</t>
-  </si>
-  <si>
-    <t>0.8118,0.2627,0.0151,0.0040</t>
+    <t>0.7465,0.1050,0.0787,0.0022</t>
+  </si>
+  <si>
+    <t>0.8113,0.2637,0.0151,0.0040</t>
   </si>
   <si>
     <t>0.0032,0.0005,0.9975,0.0004</t>
   </si>
   <si>
-    <t>0.0150,0.1946,0.8944,0.0016</t>
-  </si>
-  <si>
-    <t>0.8969,0.0044,0.0710,0.0012</t>
-  </si>
-  <si>
-    <t>0.7129,0.0122,0.2262,0.0017</t>
-  </si>
-  <si>
-    <t>0.4348,0.6584,0.0305,0.0014</t>
-  </si>
-  <si>
-    <t>0.0066,0.9660,0.5513,0.0023</t>
-  </si>
-  <si>
-    <t>0.0010,0.4857,0.9735,0.0004</t>
+    <t>0.0150,0.1956,0.8939,0.0016</t>
+  </si>
+  <si>
+    <t>0.8972,0.0045,0.0707,0.0012</t>
+  </si>
+  <si>
+    <t>0.7129,0.0123,0.2260,0.0017</t>
+  </si>
+  <si>
+    <t>0.4348,0.6586,0.0304,0.0013</t>
+  </si>
+  <si>
+    <t>0.0066,0.9662,0.5499,0.0023</t>
+  </si>
+  <si>
+    <t>0.0010,0.4878,0.9733,0.0004</t>
   </si>
   <si>
     <t>0.0017,0.0032,0.9971,0.0012</t>
   </si>
   <si>
-    <t>0.0085,0.0631,0.9730,0.0012</t>
-  </si>
-  <si>
-    <t>0.1313,0.0015,0.8798,0.0048</t>
-  </si>
-  <si>
-    <t>0.0006,0.5678,0.9599,0.0011</t>
+    <t>0.0085,0.0633,0.9730,0.0012</t>
+  </si>
+  <si>
+    <t>0.1315,0.0015,0.8796,0.0048</t>
+  </si>
+  <si>
+    <t>0.0006,0.5699,0.9597,0.0011</t>
   </si>
   <si>
     <t>0.0011,0.9870,0.0151,0.0054</t>
   </si>
   <si>
-    <t>0.0025,0.0291,0.9920,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.7605,0.0011,0.9809</t>
+    <t>0.0025,0.0292,0.9920,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.7616,0.0011,0.9807</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.0003,0.9997,0.0128,0.0006</t>
+    <t>0.0003,0.9997,0.0127,0.0006</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0061,0.0002</t>
   </si>
   <si>
-    <t>0.0003,0.0089,0.9973,0.0012</t>
-  </si>
-  <si>
-    <t>0.0007,0.1080,0.9922,0.0015</t>
-  </si>
-  <si>
-    <t>0.0067,0.0038,0.9918,0.0006</t>
-  </si>
-  <si>
-    <t>0.0203,0.0002,0.9926,0.0001</t>
+    <t>0.0003,0.0090,0.9973,0.0012</t>
+  </si>
+  <si>
+    <t>0.0007,0.1085,0.9922,0.0015</t>
+  </si>
+  <si>
+    <t>0.0067,0.0038,0.9917,0.0006</t>
+  </si>
+  <si>
+    <t>0.0204,0.0002,0.9926,0.0001</t>
   </si>
   <si>
     <t>0.0073,0.0012,0.9943,0.0001</t>
   </si>
   <si>
-    <t>0.0230,0.0118,0.9707,0.0009</t>
+    <t>0.0231,0.0118,0.9706,0.0009</t>
   </si>
   <si>
     <t>0.9754,0.0069,0.0097,0.0003</t>
   </si>
   <si>
-    <t>0.9637,0.0005,0.0329,0.0002</t>
-  </si>
-  <si>
-    <t>0.9635,0.0149,0.0142,0.0059</t>
-  </si>
-  <si>
-    <t>0.2913,0.0014,0.7829,0.0005</t>
-  </si>
-  <si>
-    <t>0.9828,0.0003,0.0113,0.0002</t>
-  </si>
-  <si>
-    <t>0.9881,0.0018,0.0054,0.0004</t>
+    <t>0.9640,0.0005,0.0326,0.0002</t>
+  </si>
+  <si>
+    <t>0.9636,0.0149,0.0142,0.0058</t>
+  </si>
+  <si>
+    <t>0.2923,0.0014,0.7819,0.0005</t>
+  </si>
+  <si>
+    <t>0.9829,0.0003,0.0112,0.0002</t>
+  </si>
+  <si>
+    <t>0.9882,0.0018,0.0053,0.0004</t>
   </si>
   <si>
     <t>0.9922,0.0008,0.0029,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.9984,0.9349,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.1236,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0142,0.9943,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.9778,0.9163,0.0005</t>
+    <t>0.0000,0.9984,0.9347,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1240,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0143,0.9943,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.9778,0.9160,0.0005</t>
   </si>
   <si>
     <t>0.0003,0.0006,0.9994,0.0003</t>
@@ -1030,25 +1036,25 @@
     <t>0.0001,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9784,0.0002,0.0233,0.0001</t>
-  </si>
-  <si>
-    <t>0.0991,0.0170,0.9047,0.0023</t>
-  </si>
-  <si>
-    <t>0.0104,0.0024,0.9927,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.7916,0.9855,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.8967,0.9847,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.4862,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9754,0.9778,0.0001</t>
+    <t>0.9785,0.0002,0.0232,0.0001</t>
+  </si>
+  <si>
+    <t>0.0995,0.0170,0.9043,0.0023</t>
+  </si>
+  <si>
+    <t>0.0104,0.0024,0.9926,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.7922,0.9854,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.8970,0.9847,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.4854,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9755,0.9777,0.0001</t>
   </si>
   <si>
     <t>0.0010,0.0021,0.0010,0.9998</t>
@@ -1063,37 +1069,37 @@
     <t>0.0020,0.0010,0.0010,0.9997</t>
   </si>
   <si>
-    <t>0.0194,0.0013,0.0029,0.9966</t>
+    <t>0.0195,0.0013,0.0029,0.9966</t>
   </si>
   <si>
     <t>0.0004,0.0017,0.0018,0.9999</t>
   </si>
   <si>
-    <t>0.0001,0.9965,0.9149,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8844,0.9943,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.8765,0.9034,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.4045,0.9940,0.0004</t>
+    <t>0.0001,0.9965,0.9146,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8849,0.9943,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.8770,0.9031,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.4058,0.9940,0.0004</t>
   </si>
   <si>
     <t>0.0000,0.9891,0.9917,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9871,0.8152,0.0002</t>
+    <t>0.0002,0.9871,0.8146,0.0002</t>
   </si>
   <si>
     <t>0.9927,0.0053,0.0008,0.0006</t>
   </si>
   <si>
-    <t>0.9817,0.0106,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.9710,0.0339,0.0011,0.0004</t>
+    <t>0.9817,0.0107,0.0038,0.0006</t>
+  </si>
+  <si>
+    <t>0.9709,0.0341,0.0011,0.0004</t>
   </si>
   <si>
     <t>0.9926,0.0034,0.0013,0.0003</t>
@@ -1105,13 +1111,13 @@
     <t>0.9924,0.0023,0.0013,0.0007</t>
   </si>
   <si>
-    <t>0.9903,0.0010,0.0032,0.0004</t>
+    <t>0.9904,0.0010,0.0032,0.0004</t>
   </si>
   <si>
     <t>0.9971,0.0022,0.0006,0.0001</t>
   </si>
   <si>
-    <t>0.9934,0.0005,0.0017,0.0004</t>
+    <t>0.9935,0.0005,0.0017,0.0004</t>
   </si>
   <si>
     <t>0.9927,0.0034,0.0014,0.0005</t>
@@ -1141,10 +1147,10 @@
     <t>0.0148,0.0013,0.9899,0.0002</t>
   </si>
   <si>
-    <t>0.9520,0.0001,0.0669,0.0000</t>
-  </si>
-  <si>
-    <t>0.0232,0.0010,0.9857,0.0001</t>
+    <t>0.9521,0.0001,0.0666,0.0000</t>
+  </si>
+  <si>
+    <t>0.0233,0.0010,0.9857,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.9997,0.0004,0.0002</t>
@@ -1153,10 +1159,10 @@
     <t>0.0001,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.2313,0.8694,0.0046,0.0009</t>
-  </si>
-  <si>
-    <t>0.0409,0.9693,0.0177,0.0035</t>
+    <t>0.2311,0.8697,0.0046,0.0009</t>
+  </si>
+  <si>
+    <t>0.0409,0.9693,0.0176,0.0035</t>
   </si>
   <si>
     <t>0.0005,0.9994,0.0005,0.0002</t>
@@ -1165,22 +1171,22 @@
     <t>0.0001,0.9999,0.0005,0.0001</t>
   </si>
   <si>
-    <t>0.6354,0.4715,0.0241,0.0010</t>
-  </si>
-  <si>
-    <t>0.0840,0.0147,0.9205,0.0034</t>
-  </si>
-  <si>
-    <t>0.0267,0.0071,0.9734,0.0009</t>
-  </si>
-  <si>
-    <t>0.2705,0.0107,0.7424,0.0028</t>
-  </si>
-  <si>
-    <t>0.0984,0.0151,0.9144,0.0038</t>
-  </si>
-  <si>
-    <t>0.0002,0.5317,0.4590,0.3203</t>
+    <t>0.6356,0.4719,0.0239,0.0010</t>
+  </si>
+  <si>
+    <t>0.0844,0.0147,0.9200,0.0034</t>
+  </si>
+  <si>
+    <t>0.0268,0.0071,0.9734,0.0009</t>
+  </si>
+  <si>
+    <t>0.2713,0.0108,0.7414,0.0028</t>
+  </si>
+  <si>
+    <t>0.0989,0.0152,0.9140,0.0038</t>
+  </si>
+  <si>
+    <t>0.0002,0.5327,0.4582,0.3202</t>
   </si>
   <si>
     <t>0.0002,0.9998,0.0012,0.0002</t>
@@ -1189,25 +1195,25 @@
     <t>0.0000,0.9999,0.0002,0.0002</t>
   </si>
   <si>
-    <t>0.0002,0.9987,0.0010,0.0132</t>
-  </si>
-  <si>
-    <t>0.0003,0.9988,0.0825,0.0021</t>
-  </si>
-  <si>
-    <t>0.0036,0.9947,0.0639,0.0005</t>
-  </si>
-  <si>
-    <t>0.5089,0.4570,0.0765,0.0035</t>
-  </si>
-  <si>
-    <t>0.2228,0.7901,0.0296,0.0070</t>
+    <t>0.0002,0.9987,0.0010,0.0131</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0822,0.0020</t>
+  </si>
+  <si>
+    <t>0.0036,0.9947,0.0637,0.0005</t>
+  </si>
+  <si>
+    <t>0.5091,0.4574,0.0761,0.0035</t>
+  </si>
+  <si>
+    <t>0.2224,0.7906,0.0295,0.0069</t>
   </si>
   <si>
     <t>0.9953,0.0004,0.0009,0.0005</t>
   </si>
   <si>
-    <t>0.9779,0.0103,0.0020,0.0039</t>
+    <t>0.9778,0.0103,0.0020,0.0039</t>
   </si>
   <si>
     <t>0.9863,0.0036,0.0025,0.0015</t>
@@ -1225,31 +1231,31 @@
     <t>0.9858,0.0022,0.0038,0.0006</t>
   </si>
   <si>
-    <t>0.9860,0.0008,0.0055,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9559,0.9653,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.3040,0.9953,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0221,0.9980,0.0004</t>
+    <t>0.9861,0.0008,0.0055,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9561,0.9652,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.3047,0.9953,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0222,0.9980,0.0004</t>
   </si>
   <si>
     <t>0.0040,0.0059,0.9953,0.0001</t>
   </si>
   <si>
-    <t>0.9330,0.0015,0.0556,0.0005</t>
-  </si>
-  <si>
-    <t>0.4328,0.3146,0.0995,0.0072</t>
-  </si>
-  <si>
-    <t>0.1446,0.0004,0.9227,0.0005</t>
-  </si>
-  <si>
-    <t>0.7729,0.0032,0.2406,0.0017</t>
+    <t>0.9331,0.0015,0.0554,0.0005</t>
+  </si>
+  <si>
+    <t>0.4320,0.3160,0.0992,0.0071</t>
+  </si>
+  <si>
+    <t>0.1449,0.0004,0.9226,0.0005</t>
+  </si>
+  <si>
+    <t>0.7734,0.0032,0.2398,0.0017</t>
   </si>
   <si>
     <t>0.0040,0.0004,0.0018,0.9993</t>
@@ -1264,55 +1270,55 @@
     <t>0.0038,0.0003,0.0015,0.9994</t>
   </si>
   <si>
-    <t>0.0001,0.9849,0.9742,0.0001</t>
-  </si>
-  <si>
-    <t>0.9686,0.0008,0.0193,0.0006</t>
-  </si>
-  <si>
-    <t>0.0130,0.9820,0.0210,0.0100</t>
+    <t>0.0001,0.9849,0.9741,0.0001</t>
+  </si>
+  <si>
+    <t>0.9687,0.0008,0.0192,0.0006</t>
+  </si>
+  <si>
+    <t>0.0129,0.9821,0.0209,0.0099</t>
   </si>
   <si>
     <t>0.9914,0.0006,0.0036,0.0001</t>
   </si>
   <si>
-    <t>0.0210,0.9791,0.0181,0.0020</t>
-  </si>
-  <si>
-    <t>0.9895,0.0013,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.8270,0.0000,0.3922,0.0000</t>
-  </si>
-  <si>
-    <t>0.7006,0.0000,0.5058,0.0000</t>
+    <t>0.0209,0.9792,0.0180,0.0020</t>
+  </si>
+  <si>
+    <t>0.9896,0.0013,0.0018,0.0017</t>
+  </si>
+  <si>
+    <t>0.8274,0.0000,0.3912,0.0000</t>
+  </si>
+  <si>
+    <t>0.7014,0.0000,0.5046,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9048,0.0005,0.0584,0.0008</t>
-  </si>
-  <si>
-    <t>0.9612,0.0197,0.0114,0.0016</t>
-  </si>
-  <si>
-    <t>0.5684,0.2394,0.0543,0.0035</t>
-  </si>
-  <si>
-    <t>0.9867,0.0009,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.9317,0.0173,0.0252,0.0015</t>
-  </si>
-  <si>
-    <t>0.2139,0.6938,0.0907,0.0287</t>
-  </si>
-  <si>
-    <t>0.8951,0.0174,0.0533,0.0012</t>
-  </si>
-  <si>
-    <t>0.9433,0.0012,0.0506,0.0004</t>
+    <t>0.9053,0.0005,0.0580,0.0008</t>
+  </si>
+  <si>
+    <t>0.9612,0.0198,0.0114,0.0016</t>
+  </si>
+  <si>
+    <t>0.5676,0.2407,0.0540,0.0035</t>
+  </si>
+  <si>
+    <t>0.9868,0.0009,0.0066,0.0001</t>
+  </si>
+  <si>
+    <t>0.9318,0.0173,0.0251,0.0015</t>
+  </si>
+  <si>
+    <t>0.2140,0.6940,0.0903,0.0286</t>
+  </si>
+  <si>
+    <t>0.8953,0.0175,0.0531,0.0012</t>
+  </si>
+  <si>
+    <t>0.9435,0.0012,0.0503,0.0004</t>
   </si>
   <si>
     <t>0.9914,0.0028,0.0021,0.0003</t>
@@ -1333,55 +1339,55 @@
     <t>0.9873,0.0041,0.0030,0.0007</t>
   </si>
   <si>
-    <t>0.9898,0.0028,0.0023,0.0003</t>
+    <t>0.9898,0.0029,0.0023,0.0003</t>
   </si>
   <si>
     <t>0.9873,0.0016,0.0033,0.0002</t>
   </si>
   <si>
-    <t>0.6686,0.3573,0.0043,0.0031</t>
-  </si>
-  <si>
-    <t>0.2665,0.7301,0.0358,0.0193</t>
-  </si>
-  <si>
-    <t>0.8634,0.1101,0.0076,0.0014</t>
-  </si>
-  <si>
-    <t>0.9101,0.0380,0.0385,0.0037</t>
-  </si>
-  <si>
-    <t>0.9820,0.0068,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.9556,0.0306,0.0088,0.0012</t>
-  </si>
-  <si>
-    <t>0.9817,0.0018,0.0092,0.0002</t>
-  </si>
-  <si>
-    <t>0.9377,0.0217,0.0239,0.0019</t>
-  </si>
-  <si>
-    <t>0.0099,0.0025,0.9938,0.0001</t>
-  </si>
-  <si>
-    <t>0.9376,0.0334,0.0132,0.0006</t>
+    <t>0.6684,0.3578,0.0043,0.0031</t>
+  </si>
+  <si>
+    <t>0.2666,0.7303,0.0356,0.0192</t>
+  </si>
+  <si>
+    <t>0.8631,0.1105,0.0076,0.0014</t>
+  </si>
+  <si>
+    <t>0.9104,0.0382,0.0383,0.0037</t>
+  </si>
+  <si>
+    <t>0.9820,0.0068,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.9555,0.0308,0.0088,0.0012</t>
+  </si>
+  <si>
+    <t>0.9818,0.0018,0.0092,0.0002</t>
+  </si>
+  <si>
+    <t>0.9378,0.0217,0.0237,0.0019</t>
+  </si>
+  <si>
+    <t>0.0100,0.0025,0.9938,0.0001</t>
+  </si>
+  <si>
+    <t>0.9376,0.0336,0.0131,0.0006</t>
   </si>
   <si>
     <t>0.0005,0.0007,0.9995,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0519,0.9928,0.0044</t>
-  </si>
-  <si>
-    <t>0.0125,0.0019,0.9907,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.1842,0.9817,0.0008</t>
-  </si>
-  <si>
-    <t>0.0016,0.0030,0.9979,0.0001</t>
+    <t>0.0003,0.0521,0.9928,0.0044</t>
+  </si>
+  <si>
+    <t>0.0126,0.0019,0.9906,0.0006</t>
+  </si>
+  <si>
+    <t>0.0022,0.1850,0.9817,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.0030,0.9978,0.0001</t>
   </si>
   <si>
     <t>0.0016,0.0002,0.9992,0.0000</t>
@@ -1390,73 +1396,73 @@
     <t>0.0116,0.0013,0.9920,0.0001</t>
   </si>
   <si>
-    <t>0.0884,0.0052,0.9323,0.0008</t>
-  </si>
-  <si>
-    <t>0.1085,0.0019,0.9314,0.0004</t>
-  </si>
-  <si>
-    <t>0.7428,0.0370,0.1753,0.0034</t>
-  </si>
-  <si>
-    <t>0.0557,0.0194,0.9237,0.0014</t>
-  </si>
-  <si>
-    <t>0.0132,0.0356,0.9633,0.0003</t>
-  </si>
-  <si>
-    <t>0.0724,0.0038,0.9449,0.0008</t>
-  </si>
-  <si>
-    <t>0.2015,0.0057,0.8365,0.0034</t>
-  </si>
-  <si>
-    <t>0.5855,0.0373,0.3178,0.0019</t>
-  </si>
-  <si>
-    <t>0.1270,0.9431,0.0106,0.0005</t>
+    <t>0.0886,0.0053,0.9321,0.0008</t>
+  </si>
+  <si>
+    <t>0.1087,0.0019,0.9312,0.0004</t>
+  </si>
+  <si>
+    <t>0.7431,0.0371,0.1748,0.0033</t>
+  </si>
+  <si>
+    <t>0.0557,0.0194,0.9235,0.0014</t>
+  </si>
+  <si>
+    <t>0.0132,0.0358,0.9631,0.0003</t>
+  </si>
+  <si>
+    <t>0.0725,0.0039,0.9448,0.0008</t>
+  </si>
+  <si>
+    <t>0.2022,0.0057,0.8357,0.0034</t>
+  </si>
+  <si>
+    <t>0.5859,0.0374,0.3171,0.0019</t>
+  </si>
+  <si>
+    <t>0.1267,0.9432,0.0105,0.0005</t>
   </si>
   <si>
     <t>0.0028,0.9971,0.0061,0.0008</t>
   </si>
   <si>
-    <t>0.0701,0.9445,0.0052,0.0025</t>
-  </si>
-  <si>
-    <t>0.9730,0.0102,0.0076,0.0003</t>
-  </si>
-  <si>
-    <t>0.4484,0.6194,0.0092,0.0010</t>
-  </si>
-  <si>
-    <t>0.3343,0.5495,0.0320,0.0008</t>
-  </si>
-  <si>
-    <t>0.9476,0.0064,0.0216,0.0004</t>
-  </si>
-  <si>
-    <t>0.3127,0.0378,0.6555,0.0140</t>
-  </si>
-  <si>
-    <t>0.1236,0.0036,0.9019,0.0032</t>
-  </si>
-  <si>
-    <t>0.4770,0.0103,0.4987,0.0036</t>
+    <t>0.0699,0.9447,0.0051,0.0025</t>
+  </si>
+  <si>
+    <t>0.9730,0.0102,0.0075,0.0003</t>
+  </si>
+  <si>
+    <t>0.4477,0.6207,0.0091,0.0010</t>
+  </si>
+  <si>
+    <t>0.3341,0.5501,0.0319,0.0008</t>
+  </si>
+  <si>
+    <t>0.9476,0.0065,0.0215,0.0004</t>
+  </si>
+  <si>
+    <t>0.3131,0.0379,0.6549,0.0140</t>
+  </si>
+  <si>
+    <t>0.1238,0.0036,0.9017,0.0032</t>
+  </si>
+  <si>
+    <t>0.4778,0.0104,0.4975,0.0036</t>
   </si>
   <si>
     <t>0.0102,0.0018,0.9918,0.0004</t>
   </si>
   <si>
-    <t>0.1499,0.0053,0.8557,0.0005</t>
-  </si>
-  <si>
-    <t>0.0378,0.0391,0.9176,0.0003</t>
+    <t>0.1500,0.0054,0.8555,0.0005</t>
+  </si>
+  <si>
+    <t>0.0378,0.0393,0.9173,0.0003</t>
   </si>
   <si>
     <t>0.0029,0.0113,0.9944,0.0007</t>
   </si>
   <si>
-    <t>0.0053,0.0072,0.9916,0.0002</t>
+    <t>0.0053,0.0072,0.9915,0.0002</t>
   </si>
   <si>
     <t>0.9927,0.0006,0.0019,0.0001</t>
@@ -1465,40 +1471,40 @@
     <t>0.9782,0.0102,0.0059,0.0010</t>
   </si>
   <si>
-    <t>0.9738,0.0097,0.0050,0.0049</t>
+    <t>0.9739,0.0097,0.0050,0.0049</t>
   </si>
   <si>
     <t>0.9861,0.0086,0.0006,0.0008</t>
   </si>
   <si>
-    <t>0.9600,0.0244,0.0099,0.0039</t>
-  </si>
-  <si>
-    <t>0.9676,0.0231,0.0062,0.0024</t>
-  </si>
-  <si>
-    <t>0.9886,0.0072,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.9913,0.0012,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.0083,0.0028,0.9936,0.0005</t>
-  </si>
-  <si>
-    <t>0.0602,0.0176,0.9278,0.0010</t>
-  </si>
-  <si>
-    <t>0.4231,0.0042,0.5905,0.0121</t>
-  </si>
-  <si>
-    <t>0.0021,0.0008,0.9985,0.0001</t>
+    <t>0.9599,0.0245,0.0098,0.0039</t>
+  </si>
+  <si>
+    <t>0.9676,0.0233,0.0062,0.0024</t>
+  </si>
+  <si>
+    <t>0.9886,0.0073,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.9914,0.0012,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.0083,0.0028,0.9935,0.0005</t>
+  </si>
+  <si>
+    <t>0.0604,0.0177,0.9274,0.0010</t>
+  </si>
+  <si>
+    <t>0.4237,0.0042,0.5898,0.0121</t>
+  </si>
+  <si>
+    <t>0.0021,0.0009,0.9984,0.0001</t>
   </si>
   <si>
     <t>0.0003,0.0022,0.9992,0.0001</t>
   </si>
   <si>
-    <t>0.0049,0.0156,0.9903,0.0005</t>
+    <t>0.0049,0.0157,0.9903,0.0005</t>
   </si>
   <si>
     <t>0.0003,0.0001,0.9998,0.0000</t>
@@ -1513,19 +1519,19 @@
     <t>0.0037,0.0065,0.9947,0.0003</t>
   </si>
   <si>
-    <t>0.0439,0.0109,0.9515,0.0020</t>
-  </si>
-  <si>
-    <t>0.7290,0.0017,0.3200,0.0013</t>
-  </si>
-  <si>
-    <t>0.4238,0.0012,0.6012,0.0059</t>
-  </si>
-  <si>
-    <t>0.9347,0.0087,0.0332,0.0003</t>
-  </si>
-  <si>
-    <t>0.9930,0.0020,0.0010,0.0001</t>
+    <t>0.0439,0.0109,0.9514,0.0020</t>
+  </si>
+  <si>
+    <t>0.7300,0.0017,0.3187,0.0013</t>
+  </si>
+  <si>
+    <t>0.4245,0.0012,0.6006,0.0059</t>
+  </si>
+  <si>
+    <t>0.9348,0.0088,0.0331,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0020,0.0010,0.0001</t>
   </si>
   <si>
     <t>0.9857,0.0120,0.0011,0.0009</t>
@@ -1534,7 +1540,7 @@
     <t>0.9922,0.0033,0.0014,0.0002</t>
   </si>
   <si>
-    <t>0.9495,0.0322,0.0084,0.0014</t>
+    <t>0.9495,0.0324,0.0084,0.0014</t>
   </si>
   <si>
     <t>0.9909,0.0014,0.0022,0.0002</t>
@@ -1543,43 +1549,43 @@
     <t>0.9851,0.0098,0.0027,0.0007</t>
   </si>
   <si>
-    <t>0.9937,0.0021,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9822,0.0024,0.0054,0.0021</t>
-  </si>
-  <si>
-    <t>0.0077,0.0189,0.9854,0.0004</t>
+    <t>0.9938,0.0021,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9823,0.0024,0.0054,0.0021</t>
+  </si>
+  <si>
+    <t>0.0077,0.0190,0.9854,0.0004</t>
   </si>
   <si>
     <t>0.0010,0.0033,0.9988,0.0000</t>
   </si>
   <si>
-    <t>0.0021,0.0019,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0109,0.0295,0.9723,0.0005</t>
+    <t>0.0021,0.0019,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0109,0.0296,0.9722,0.0005</t>
   </si>
   <si>
     <t>0.0104,0.0018,0.9921,0.0001</t>
   </si>
   <si>
-    <t>0.7324,0.0467,0.1258,0.0080</t>
-  </si>
-  <si>
-    <t>0.0736,0.0238,0.9045,0.0057</t>
+    <t>0.7329,0.0472,0.1252,0.0080</t>
+  </si>
+  <si>
+    <t>0.0739,0.0239,0.9039,0.0057</t>
   </si>
   <si>
     <t>0.0019,0.0008,0.9977,0.0009</t>
   </si>
   <si>
-    <t>0.9583,0.0007,0.0062,0.0065</t>
+    <t>0.9584,0.0008,0.0062,0.0064</t>
   </si>
   <si>
     <t>0.0006,0.0018,0.0002,0.9999</t>
   </si>
   <si>
-    <t>0.0074,0.0002,0.0010,0.9992</t>
+    <t>0.0075,0.0002,0.0010,0.9992</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.0020,1.0000</t>
@@ -1588,7 +1594,7 @@
     <t>0.0002,0.0002,0.0009,1.0000</t>
   </si>
   <si>
-    <t>0.6963,0.0093,0.0176,0.2278</t>
+    <t>0.6972,0.0093,0.0176,0.2266</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1980,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1988,7 +1994,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2002,7 +2008,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2016,7 +2022,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2030,7 +2036,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2044,7 +2050,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2058,7 +2064,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2072,7 +2078,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2086,7 +2092,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2100,7 +2106,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2114,7 +2120,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2128,7 +2134,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2142,7 +2148,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2156,7 +2162,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2170,7 +2176,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2184,7 +2190,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2198,7 +2204,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2212,7 +2218,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2226,7 +2232,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2240,7 +2246,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2254,7 +2260,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2268,7 +2274,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2282,7 +2288,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2296,7 +2302,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2310,7 +2316,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2324,7 +2330,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2338,7 +2344,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2352,7 +2358,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2366,7 +2372,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2380,7 +2386,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2394,7 +2400,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2408,7 +2414,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2422,7 +2428,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2436,7 +2442,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2450,7 +2456,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2464,7 +2470,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2478,7 +2484,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2492,7 +2498,7 @@
         <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2506,7 +2512,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2520,7 +2526,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2534,7 +2540,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2548,7 +2554,7 @@
         <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2562,7 +2568,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2576,7 +2582,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2590,7 +2596,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2604,7 +2610,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2618,7 +2624,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2632,7 +2638,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2646,7 +2652,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2660,7 +2666,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2674,7 +2680,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2688,7 +2694,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2702,7 +2708,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2716,7 +2722,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2730,7 +2736,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2744,7 +2750,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2758,7 +2764,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2772,7 +2778,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2786,7 +2792,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2800,7 +2806,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2814,7 +2820,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2828,7 +2834,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2842,7 +2848,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2856,7 +2862,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2870,7 +2876,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2884,7 +2890,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2898,7 +2904,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2912,7 +2918,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2926,7 +2932,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2940,7 +2946,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2954,7 +2960,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2968,7 +2974,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2982,7 +2988,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2996,7 +3002,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3010,7 +3016,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3024,7 +3030,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3038,7 +3044,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3052,7 +3058,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3066,7 +3072,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3080,7 +3086,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3094,7 +3100,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3108,7 +3114,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3122,7 +3128,7 @@
         <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3136,7 +3142,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3150,7 +3156,7 @@
         <v>266</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3164,7 +3170,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3178,7 +3184,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3192,7 +3198,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3206,7 +3212,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3220,7 +3226,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3234,7 +3240,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3248,7 +3254,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3262,7 +3268,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3276,7 +3282,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3290,7 +3296,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3304,7 +3310,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3318,7 +3324,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3332,7 +3338,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3346,7 +3352,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3360,7 +3366,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3374,7 +3380,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3388,7 +3394,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3402,7 +3408,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3416,7 +3422,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3430,7 +3436,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3444,7 +3450,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3458,7 +3464,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3472,7 +3478,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3486,7 +3492,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3500,7 +3506,7 @@
         <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3514,7 +3520,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3528,7 +3534,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3542,7 +3548,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3556,7 +3562,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3570,7 +3576,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3584,7 +3590,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3598,7 +3604,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3612,7 +3618,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3626,7 +3632,7 @@
         <v>267</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3640,7 +3646,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3654,7 +3660,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3668,7 +3674,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3682,7 +3688,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3696,7 +3702,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3710,7 +3716,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3724,7 +3730,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3738,7 +3744,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3752,7 +3758,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3766,7 +3772,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3780,7 +3786,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3794,7 +3800,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3808,7 +3814,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3822,7 +3828,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3836,7 +3842,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3850,7 +3856,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3864,7 +3870,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3878,7 +3884,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3892,7 +3898,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3906,7 +3912,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,10 +3923,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3934,7 +3940,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3948,7 +3954,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3962,7 +3968,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3976,7 +3982,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3990,7 +3996,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4004,7 +4010,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4018,7 +4024,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4032,7 +4038,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4046,7 +4052,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4060,7 +4066,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4074,7 +4080,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4088,7 +4094,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4102,7 +4108,7 @@
         <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4113,10 +4119,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4130,7 +4136,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4144,7 +4150,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4158,7 +4164,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4172,7 +4178,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4186,7 +4192,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4200,7 +4206,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4214,7 +4220,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4228,7 +4234,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4242,7 +4248,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4256,7 +4262,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4270,7 +4276,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4284,7 +4290,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4298,7 +4304,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4312,7 +4318,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4326,7 +4332,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4340,7 +4346,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4354,7 +4360,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4368,7 +4374,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4382,7 +4388,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4396,7 +4402,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4410,7 +4416,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4424,7 +4430,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4438,7 +4444,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4452,7 +4458,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4466,7 +4472,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4480,7 +4486,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4494,7 +4500,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4508,7 +4514,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4522,7 +4528,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4536,7 +4542,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4550,7 +4556,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4564,7 +4570,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4578,7 +4584,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4592,7 +4598,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4606,7 +4612,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4620,7 +4626,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4634,7 +4640,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4648,7 +4654,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4662,7 +4668,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4676,7 +4682,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4690,7 +4696,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4704,7 +4710,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4718,7 +4724,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4732,7 +4738,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4746,7 +4752,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4760,7 +4766,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4774,7 +4780,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4788,7 +4794,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4802,7 +4808,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4816,7 +4822,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4830,7 +4836,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,10 +4847,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4858,7 +4864,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4872,7 +4878,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4886,7 +4892,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4900,7 +4906,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4914,7 +4920,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4928,7 +4934,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4942,7 +4948,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4956,7 +4962,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4970,7 +4976,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4984,7 +4990,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4998,7 +5004,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5012,7 +5018,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5026,7 +5032,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5040,7 +5046,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5054,7 +5060,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5068,7 +5074,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5082,7 +5088,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5096,7 +5102,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5110,7 +5116,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5124,7 +5130,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5138,7 +5144,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5152,7 +5158,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5166,7 +5172,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5180,7 +5186,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5194,7 +5200,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5208,7 +5214,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5222,7 +5228,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5236,7 +5242,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5250,7 +5256,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5264,7 +5270,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5278,7 +5284,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5292,7 +5298,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5306,7 +5312,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5320,7 +5326,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5334,7 +5340,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5348,7 +5354,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5362,7 +5368,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5376,7 +5382,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5390,7 +5396,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5404,7 +5410,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5418,7 +5424,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5432,7 +5438,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5446,7 +5452,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5460,7 +5466,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5474,7 +5480,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5488,7 +5494,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5502,7 +5508,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5516,7 +5522,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5530,7 +5536,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
